--- a/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
+++ b/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:39:31+00:00</t>
+    <t>2026-09-03T14:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
+++ b/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:38:58+00:00</t>
+    <t>2026-09-04T10:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -86,8 +86,8 @@
   <si>
     <t>IHE-PaLM - Laboratory Specialty Section
  - Une section de premier niveau est appelée 'Chapitre' et correspond à une sous-discipline de la biologie médicale (par exemple « biochimie »). Elle contient :
-  - soit directement la présentation des résultats d'examens de biologie médicale obtenus pour ce chapitre : dans ce cas, il y a un unique élément &lt;text&gt; (présentation du contenu pour le lecteur) et un unique élément &lt;entry&gt; (données codées pour les SIS dont procède le contenu de l'élément &lt;text&gt;)
-  - soit une liste de sections de second niveau, appelés sous-chapitres (par exemple « Gaz du sang ») : dans ce cas, il y a une liste d'éléments &lt;component&gt; dont chacun introduit une &lt;section&gt; de second niveau présentant un sous-ensemble de un ou plusieurs résultats d'examens de biologie médicale.Remarque : L'arborescence du corps du compte rendu d'examens de biologie médicale est choisie par le LPS producteur du document selon la logique de présentation définie par le laboratoire.</t>
+  - soit directement la présentation des résultats d'examens de biologie médicale obtenus pour ce chapitre : dans ce cas, il y a un unique élément `&lt;text&gt;` (présentation du contenu pour le lecteur) et un unique élément `&lt;entry&gt;` (données codées pour les SIS dont procède le contenu de l'élément `&lt;text&gt;`)
+  - soit une liste de sections de second niveau, appelés sous-chapitres (par exemple « Gaz du sang ») : dans ce cas, il y a une liste d'éléments `&lt;component&gt;` dont chacun introduit une `&lt;section&gt;` de second niveau présentant un sous-ensemble de un ou plusieurs résultats d'examens de biologie médicale.Remarque : L'arborescence du corps du compte rendu d'examens de biologie médicale est choisie par le LPS producteur du document selon la logique de présentation définie par le laboratoire.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
+++ b/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:07:56+00:00</t>
+    <t>2026-09-08T08:30:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
+++ b/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T08:30:09+00:00</t>
+    <t>2026-09-10T13:09:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
